--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0.8294229333851104</v>
+        <v>0.7091389668511001</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.01077844311377246</v>
+        <v>0.01010479041916168</v>
       </c>
       <c r="H3">
-        <v>0.8563960369098295</v>
+        <v>0.754889867938268</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
@@ -653,16 +653,16 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4.998278023880774</v>
+        <v>4.976653764861889</v>
       </c>
       <c r="F2">
-        <v>4.985275620044693</v>
+        <v>4.965563109983805</v>
       </c>
       <c r="G2">
-        <v>4.986890142865329</v>
+        <v>4.961095809955378</v>
       </c>
       <c r="H2">
-        <v>-0.01300240383607996</v>
+        <v>-0.01109065487808502</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -688,16 +688,16 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>4.998598823765548</v>
+        <v>4.957988261063507</v>
       </c>
       <c r="F3">
-        <v>4.971187985955314</v>
+        <v>4.934058033997839</v>
       </c>
       <c r="G3">
-        <v>4.975147981279103</v>
+        <v>4.926596308561679</v>
       </c>
       <c r="H3">
-        <v>-0.02741083781023301</v>
+        <v>-0.02393022706566796</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -723,16 +723,16 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>4.999959926425509</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>4.960479215403539</v>
+        <v>4.960499375821997</v>
       </c>
       <c r="G4">
-        <v>4.966704885370398</v>
+        <v>4.966736316481682</v>
       </c>
       <c r="H4">
-        <v>-0.03948071102196952</v>
+        <v>-0.03950062417800296</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -793,16 +793,16 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>4.99844040009008</v>
+        <v>4.948566654047381</v>
       </c>
       <c r="F6">
-        <v>4.989948398719691</v>
+        <v>4.940850418673874</v>
       </c>
       <c r="G6">
-        <v>4.990949245009655</v>
+        <v>4.927824273889328</v>
       </c>
       <c r="H6">
-        <v>-0.00849200137038833</v>
+        <v>-0.007716235373507908</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -828,16 +828,16 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4.959419223945099</v>
       </c>
       <c r="F7">
-        <v>4.998378256273359</v>
+        <v>4.957886397575694</v>
       </c>
       <c r="G7">
-        <v>4.998634321072302</v>
+        <v>4.946729119109198</v>
       </c>
       <c r="H7">
-        <v>-0.001621743726641217</v>
+        <v>-0.00153282636940477</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -863,16 +863,16 @@
         <v>4.767886457146448</v>
       </c>
       <c r="E8">
-        <v>4.997562294599462</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>4.725489080903173</v>
+        <v>4.727035904034575</v>
       </c>
       <c r="G8">
-        <v>4.767903070359075</v>
+        <v>4.770135498134379</v>
       </c>
       <c r="H8">
-        <v>-0.2720732136962898</v>
+        <v>-0.2729640959654251</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
@@ -544,16 +544,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.2756348321385929</v>
+        <v>-0.2125665025966779</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="H2">
-        <v>0.7091389668511001</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.01010479041916168</v>
+        <v>0.01411589895988113</v>
       </c>
       <c r="H3">
-        <v>0.754889867938268</v>
+        <v>0.9780219780219781</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
@@ -653,16 +653,16 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4.976653764861889</v>
+        <v>4.974941781899233</v>
       </c>
       <c r="F2">
-        <v>4.965563109983805</v>
+        <v>4.964900060366543</v>
       </c>
       <c r="G2">
-        <v>4.961095809955378</v>
+        <v>4.960198336359883</v>
       </c>
       <c r="H2">
-        <v>-0.01109065487808502</v>
+        <v>-0.01004172153268985</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -688,16 +688,16 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>4.957988261063507</v>
+        <v>4.955225958512578</v>
       </c>
       <c r="F3">
-        <v>4.934058033997839</v>
+        <v>4.932095428002538</v>
       </c>
       <c r="G3">
-        <v>4.926596308561679</v>
+        <v>4.924063703739858</v>
       </c>
       <c r="H3">
-        <v>-0.02393022706566796</v>
+        <v>-0.02313053051004105</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -723,7 +723,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4.998670385746197</v>
       </c>
       <c r="F4">
         <v>4.960499375821997</v>
@@ -732,7 +732,7 @@
         <v>4.966736316481682</v>
       </c>
       <c r="H4">
-        <v>-0.03950062417800296</v>
+        <v>-0.03817100992420026</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4.999585399417387</v>
       </c>
       <c r="F5">
         <v>4.99949485269799</v>
@@ -767,7 +767,7 @@
         <v>4.999574612798307</v>
       </c>
       <c r="H5">
-        <v>-0.0005051473020096821</v>
+        <v>-9.054671939714867E-05</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -793,25 +793,25 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>4.948566654047381</v>
+        <v>4.942549616918525</v>
       </c>
       <c r="F6">
-        <v>4.940850418673874</v>
+        <v>4.936918875966986</v>
       </c>
       <c r="G6">
-        <v>4.927824273889328</v>
+        <v>4.922757623664916</v>
       </c>
       <c r="H6">
-        <v>-0.007716235373507908</v>
+        <v>-0.00563074095153967</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -828,16 +828,16 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>4.959419223945099</v>
+        <v>4.958463466162237</v>
       </c>
       <c r="F7">
-        <v>4.957886397575694</v>
+        <v>4.957126307985793</v>
       </c>
       <c r="G7">
-        <v>4.946729119109198</v>
+        <v>4.945755254322136</v>
       </c>
       <c r="H7">
-        <v>-0.00153282636940477</v>
+        <v>-0.001337158176443554</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -863,7 +863,7 @@
         <v>4.767886457146448</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4.928828552012787</v>
       </c>
       <c r="F8">
         <v>4.727035904034575</v>
@@ -872,7 +872,7 @@
         <v>4.770135498134379</v>
       </c>
       <c r="H8">
-        <v>-0.2729640959654251</v>
+        <v>-0.2017926479782119</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4.998570487482159</v>
       </c>
       <c r="F9">
         <v>4.995004340053581</v>
@@ -907,7 +907,7 @@
         <v>4.995793128466173</v>
       </c>
       <c r="H9">
-        <v>-0.004995659946419205</v>
+        <v>-0.003566147428578261</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4.999942246288397</v>
       </c>
       <c r="F10">
         <v>4.999916986385888</v>
@@ -942,7 +942,7 @@
         <v>4.999930093798643</v>
       </c>
       <c r="H10">
-        <v>-8.301361411145513E-05</v>
+        <v>-2.525990250788519E-05</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>4.708382756536059</v>
+        <v>4.69497046162264</v>
       </c>
       <c r="F12">
         <v>4.656155923149405</v>
@@ -1012,10 +1012,10 @@
         <v>4.588574519081727</v>
       </c>
       <c r="H12">
-        <v>-0.05222683338665295</v>
+        <v>-0.03881453847323472</v>
       </c>
       <c r="I12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12">
         <v>27</v>
@@ -1038,7 +1038,7 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4.999851702621107</v>
       </c>
       <c r="F13">
         <v>4.999723287952962</v>
@@ -1047,7 +1047,7 @@
         <v>4.99976697932881</v>
       </c>
       <c r="H13">
-        <v>-0.0002767120470381838</v>
+        <v>-0.0001284146681448491</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>40</v>
       </c>
       <c r="B15">
-        <v>3.400003040207932</v>
+        <v>3.400002682974573</v>
       </c>
       <c r="C15">
         <v>3.400002682974573</v>
@@ -1108,7 +1108,7 @@
         <v>2.950003437561171</v>
       </c>
       <c r="E15">
-        <v>3.919512295329886</v>
+        <v>3.855648372344918</v>
       </c>
       <c r="F15">
         <v>3.864440452438402</v>
@@ -1117,10 +1117,10 @@
         <v>3.571635970349212</v>
       </c>
       <c r="H15">
-        <v>-0.05507184289148282</v>
+        <v>0.008792080093484731</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
@@ -538,7 +538,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>42840</v>
+        <v>42748</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>42840</v>
+        <v>42748</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -653,16 +653,16 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4.974941781899233</v>
+        <v>4.974752009421024</v>
       </c>
       <c r="F2">
-        <v>4.964900060366543</v>
+        <v>4.964634239289306</v>
       </c>
       <c r="G2">
-        <v>4.960198336359883</v>
+        <v>4.959896907889774</v>
       </c>
       <c r="H2">
-        <v>-0.01004172153268985</v>
+        <v>-0.01011777013171912</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -688,16 +688,16 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>4.955225958512578</v>
+        <v>4.954886872916855</v>
       </c>
       <c r="F3">
-        <v>4.932095428002538</v>
+        <v>4.93178496289583</v>
       </c>
       <c r="G3">
-        <v>4.924063703739858</v>
+        <v>4.923660234259316</v>
       </c>
       <c r="H3">
-        <v>-0.02313053051004105</v>
+        <v>-0.02310191002102519</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -793,16 +793,16 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>4.942549616918525</v>
+        <v>4.942114530052909</v>
       </c>
       <c r="F6">
-        <v>4.936918875966986</v>
+        <v>4.93648979343922</v>
       </c>
       <c r="G6">
-        <v>4.922757623664916</v>
+        <v>4.922213613076152</v>
       </c>
       <c r="H6">
-        <v>-0.00563074095153967</v>
+        <v>-0.005624736613689755</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -828,16 +828,16 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>4.958463466162237</v>
+        <v>4.958148899063696</v>
       </c>
       <c r="F7">
-        <v>4.957126307985793</v>
+        <v>4.956801614236591</v>
       </c>
       <c r="G7">
-        <v>4.945755254322136</v>
+        <v>4.945344444591945</v>
       </c>
       <c r="H7">
-        <v>-0.001337158176443554</v>
+        <v>-0.0013472848271048</v>
       </c>
       <c r="I7">
         <v>0</v>
